--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.39282222141888</v>
+        <v>8.188833610980568</v>
       </c>
       <c r="D2" t="n">
-        <v>50.36372678837312</v>
+        <v>8.184105603110632</v>
       </c>
       <c r="E2" t="n">
-        <v>18.33982387829073</v>
+        <v>2.980221380222243</v>
       </c>
       <c r="F2" t="n">
-        <v>18.55814064278726</v>
+        <v>3.015697854452929</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.08640086685399</v>
+        <v>2.776540140863773</v>
       </c>
       <c r="D3" t="n">
-        <v>26.74412289907507</v>
+        <v>4.3459199710997</v>
       </c>
       <c r="E3" t="n">
-        <v>18.33982387829073</v>
+        <v>2.980221380222243</v>
       </c>
       <c r="F3" t="n">
-        <v>18.55814064278726</v>
+        <v>3.015697854452929</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69700614760582</v>
+        <v>6.938263498985946</v>
       </c>
       <c r="D4" t="n">
-        <v>43.37834950205099</v>
+        <v>7.048981794083287</v>
       </c>
       <c r="E4" t="n">
-        <v>18.33982387829073</v>
+        <v>2.980221380222243</v>
       </c>
       <c r="F4" t="n">
-        <v>18.55814064278726</v>
+        <v>3.015697854452929</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.13784585368887</v>
+        <v>4.409899951224441</v>
       </c>
       <c r="D5" t="n">
-        <v>16.28314217310955</v>
+        <v>2.646010603130303</v>
       </c>
       <c r="E5" t="n">
-        <v>18.33982387829073</v>
+        <v>2.980221380222243</v>
       </c>
       <c r="F5" t="n">
-        <v>18.55814064278726</v>
+        <v>3.015697854452929</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.61507293743333</v>
+        <v>11.47494935233292</v>
       </c>
       <c r="D6" t="n">
-        <v>70.93981390575344</v>
+        <v>11.52771975968493</v>
       </c>
       <c r="E6" t="n">
-        <v>18.33982387829073</v>
+        <v>2.980221380222243</v>
       </c>
       <c r="F6" t="n">
-        <v>18.55814064278726</v>
+        <v>3.015697854452929</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.00733249809124</v>
+        <v>3.738691530939827</v>
       </c>
       <c r="D7" t="n">
-        <v>23.74248497664889</v>
+        <v>3.858153808705445</v>
       </c>
       <c r="E7" t="n">
-        <v>18.33982387829073</v>
+        <v>2.980221380222243</v>
       </c>
       <c r="F7" t="n">
-        <v>18.55814064278726</v>
+        <v>3.015697854452929</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
